--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-location.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-location.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -458,7 +458,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0</t>
   </si>
   <si>
     <t>Location.meta.security</t>
@@ -626,7 +626,7 @@
     <t>typeChambre</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-type-chambre|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-type-chambre|2.2.0}
 </t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>positionLit</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-position-lit|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-position-lit|2.2.0}
 </t>
   </si>
   <si>
@@ -816,7 +816,7 @@
     <t>Indicates the type of function performed at the location.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -1418,7 +1418,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.13671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1433,7 +1433,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.3125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
